--- a/docs/Reparto-costos-y-plan.xlsx
+++ b/docs/Reparto-costos-y-plan.xlsx
@@ -9,12 +9,13 @@
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Pagos únicos" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Pagos anuales" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Mensual" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Supuestos" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Decisiones" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Fases" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Precios" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Pagos únicos" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Pagos anuales" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Mensual" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Supuestos" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Decisiones" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Fases" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="250">
   <si>
     <t xml:space="preserve">Costos del primer año (USD)</t>
   </si>
@@ -67,6 +68,237 @@
     <t xml:space="preserve">Si se eligiera Opus 5.5 para la IA, sumar unos USD 200 a 400 al mes con 100 conductores (decisión: Sonnet 5.5 + Haiku 5.5).</t>
   </si>
   <si>
+    <t xml:space="preserve">Precio de suscripción propuesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precios en pesos chilenos, más IVA. Azul = supuesto que puedes cambiar. El resto se calcula solo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supuesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de cambio (CLP por USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dólar observado aprox. sept-2026 (Banco Central). Actualizar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo fijo mensual de la plataforma (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supabase Pro + servidor + VPS + anuales prorrateados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo variable por conductor al mes (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base de datos, IA, llamadas, correos y direcciones (de la hoja Mensual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión de cobro con tarjeta (Flow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,95% + IVA (fuente secundaria)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregas incluidas por conductor al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso justo; sobre eso se cobra el excedente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para quién</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio mensual (CLP + IVA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cómo se cobra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivale en USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incluye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prueba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validar sin riesgo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 días gratis, hasta 5 conductores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasta 5 conductores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monto fijo mensual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo, incluido el asistente de IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 a 49 conductores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por conductor activo al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 o más conductores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por conductor activo; contrato anual con pago mensual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo + soporte prioritario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregas extra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sobre el uso justo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por cada 100 entregas sobre lo incluido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pago anual: 2 meses gratis (pagas 10). Conductor activo = el que inició al menos una ruta en el mes. Receptores y administradores: ilimitados y sin costo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conductores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso mensual (CLP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo mensual (CLP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen mensual (CLP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 cliente Pyme (validación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 clientes Pyme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 cliente Flota de 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 clientes de 10 (meta SPEC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 cliente Empresa de 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El costo incluye toda la plataforma (fijo) como si hubiera un solo escenario activo. No incluye tu sueldo, soporte ni impuestos a la renta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clientes Pyme necesarios para cubrir el costo fijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo por entrega para tu cliente (Flota, 20 entregas al día, 24 días)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competencia (referencia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio publicado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tookan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$29–100 por usuario al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por usuario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shipday.com (comparativa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circuit for Teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$100–1.000 al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por volumen de paradas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">costbench.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onfleet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$299–1.300 al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por volumen de entregas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gratis hasta 300 pedidos al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por pedidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shipday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SimpliRoute (Chile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde ~US$40 (sin detalle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capterra.es</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pagos únicos (USD)</t>
   </si>
   <si>
@@ -82,9 +314,6 @@
     <t xml:space="preserve">Cuándo se paga</t>
   </si>
   <si>
-    <t xml:space="preserve">Fuente</t>
-  </si>
-  <si>
     <t xml:space="preserve">Licencia plugin de GPS (Transistorsoft Starter)</t>
   </si>
   <si>
@@ -280,22 +509,10 @@
     <t xml:space="preserve">Dato</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conductores</t>
-  </si>
-  <si>
     <t xml:space="preserve">Escenario de escala</t>
   </si>
   <si>
     <t xml:space="preserve">Entregas por conductor al día</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supuesto</t>
   </si>
   <si>
     <t xml:space="preserve">Días hábiles al mes</t>
@@ -566,12 +783,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
-    <numFmt numFmtId="168" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="&quot;US$&quot;#,##0"/>
+    <numFmt numFmtId="168" formatCode="&quot;US$&quot;0.00"/>
+    <numFmt numFmtId="169" formatCode="0.00%"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="172" formatCode="#,##0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -648,7 +869,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -664,7 +885,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCEBC0"/>
-        <bgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFFFF2B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2B3"/>
+        <bgColor rgb="FFFCEBC0"/>
       </patternFill>
     </fill>
   </fills>
@@ -711,11 +938,47 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -725,31 +988,67 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -760,11 +1059,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -772,11 +1071,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -809,7 +1108,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFCEBC0"/>
+      <rgbColor rgb="FFFFF2B3"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -826,7 +1125,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFCEBC0"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1035,129 +1334,129 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <f aca="false">'Pagos únicos'!B6</f>
         <v>424</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <f aca="false">'Pagos anuales'!B7</f>
         <v>111</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <f aca="false">12*Mensual!C13</f>
         <v>516</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <f aca="false">B5+C5+D5</f>
         <v>1051</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <f aca="false">C5+D5</f>
         <v>627</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <f aca="false">'Pagos únicos'!B6</f>
         <v>424</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <f aca="false">'Pagos anuales'!B7</f>
         <v>111</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <f aca="false">12*Mensual!D13</f>
         <v>2700</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <f aca="false">B6+C6+D6</f>
         <v>3235</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <f aca="false">C6+D6</f>
         <v>2811</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <f aca="false">'Pagos únicos'!B6</f>
         <v>424</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <f aca="false">'Pagos anuales'!B7</f>
         <v>111</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <f aca="false">12*Mensual!E13</f>
         <v>4656</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <f aca="false">B7+C7+D7</f>
         <v>5191</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <f aca="false">C7+D7</f>
         <v>4767</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <f aca="false">Mensual!E13/Supuestos!B4</f>
         <v>3.88</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1177,83 +1476,468 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="32"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="9" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="9" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="B5" s="14" t="n">
+        <v>940</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="11" t="n">
-        <v>399</v>
-      </c>
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="B6" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="10" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="B7" s="16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="11" t="n">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="10" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="B9" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="6" t="n">
-        <f aca="false">SUM(B4:B5)</f>
-        <v>424</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <f aca="false">C12/$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>59990</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <f aca="false">C13/$B$5</f>
+        <v>63.8191489361702</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>10990</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <f aca="false">C14/$B$5</f>
+        <v>11.6914893617021</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>8490</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <f aca="false">C15/$B$5</f>
+        <v>9.03191489361702</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>2990</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="20" t="n">
+        <f aca="false">C16/$B$5</f>
+        <v>3.18085106382979</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="22" t="n">
+        <f aca="false">C13</f>
+        <v>59990</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <f aca="false">($B$6+B20*$B$7)*$B$5+C20*$B$8</f>
+        <v>92815.649</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <f aca="false">C20-D20</f>
+        <v>-32825.649</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <f aca="false">IF(C20=0,0,E20/C20)</f>
+        <v>-0.547185347557926</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="22" t="n">
+        <f aca="false">3*C13</f>
+        <v>179970</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <f aca="false">($B$6+B21*$B$7)*$B$5+C21*$B$8</f>
+        <v>128046.947</v>
+      </c>
+      <c r="E21" s="23" t="n">
+        <f aca="false">C21-D21</f>
+        <v>51923.053</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <f aca="false">IF(C21=0,0,E21/C21)</f>
+        <v>0.288509490470634</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="22" t="n">
+        <f aca="false">20*C14</f>
+        <v>219800</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <f aca="false">($B$6+B22*$B$7)*$B$5+C22*$B$8</f>
+        <v>144954.98</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <f aca="false">C22-D22</f>
+        <v>74845.02</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <f aca="false">IF(C22=0,0,E22/C22)</f>
+        <v>0.340514194722475</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" s="22" t="n">
+        <f aca="false">100*C14</f>
+        <v>1099000</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <f aca="false">($B$6+B23*$B$7)*$B$5+C23*$B$8</f>
+        <v>423974.9</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <f aca="false">C23-D23</f>
+        <v>675025.1</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <f aca="false">IF(C23=0,0,E23/C23)</f>
+        <v>0.614217561419472</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" s="22" t="n">
+        <f aca="false">100*C15</f>
+        <v>849000</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <f aca="false">($B$6+B24*$B$7)*$B$5+C24*$B$8</f>
+        <v>415199.9</v>
+      </c>
+      <c r="E24" s="23" t="n">
+        <f aca="false">C24-D24</f>
+        <v>433800.1</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <f aca="false">IF(C24=0,0,E24/C24)</f>
+        <v>0.51095418138987</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="25" t="n">
+        <f aca="false">ROUNDUP(($B$6*$B$5)/(C13*(1-$B$8)-5*$B$7*$B$5),0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="26" t="n">
+        <f aca="false">C14/(20*24)</f>
+        <v>22.8958333333333</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1271,126 +1955,83 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="36"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="11" t="n">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="29" t="n">
+        <v>399</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>199</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <f aca="false">SUMIFS(B4:B6,C4:C6,"Sí")</f>
-        <v>111</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <f aca="false">SUM(B4:B6)</f>
-        <v>310</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="B5" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <f aca="false">SUM(B4:B5)</f>
+        <v>424</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1408,275 +2049,126 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="E4" s="11" t="n">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="29" t="n">
+        <v>99</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="D4" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="6" t="n">
-        <f aca="false">SUM(C4:C12)</f>
-        <v>43</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <f aca="false">SUM(D4:D12)</f>
-        <v>225</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <f aca="false">SUM(E4:E12)</f>
-        <v>388</v>
-      </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>81</v>
-      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <f aca="false">SUMIFS(B4:B6,C4:C6,"Sí")</f>
+        <v>111</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <f aca="false">SUM(B4:B6)</f>
+        <v>310</v>
+      </c>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1694,117 +2186,274 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="14" t="n">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>110</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>80</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>120</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="15" t="n">
-        <f aca="false">B4*B5*B6</f>
-        <v>48000</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>100</v>
+      <c r="E7" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="7" t="n">
+        <f aca="false">SUM(C4:C12)</f>
+        <v>43</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <f aca="false">SUM(D4:D12)</f>
+        <v>225</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <f aca="false">SUM(E4:E12)</f>
+        <v>388</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1823,168 +2472,117 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>137</v>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="33" t="n">
+        <f aca="false">B4*B5*B6</f>
+        <v>48000</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2003,159 +2601,339 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>177</v>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
